--- a/branches/fix/page-hierarchy/StructureDefinition-mii-ex-dokument-nlp-processing-status.xlsx
+++ b/branches/fix/page-hierarchy/StructureDefinition-mii-ex-dokument-nlp-processing-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T15:28:08+00:00</t>
+    <t>2026-09-04T15:37:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
